--- a/output/supplementary/P1_Fig1D_sankey_data.xlsx
+++ b/output/supplementary/P1_Fig1D_sankey_data.xlsx
@@ -6131,7 +6131,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>510(k)</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -14189,7 +14189,7 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>510(k)</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
@@ -18779,7 +18779,7 @@
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>De Novo</t>
         </is>
       </c>
       <c r="B1081" t="inlineStr">
